--- a/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_parts_list_clean_v2_20260416.xlsx
+++ b/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_parts_list_clean_v2_20260416.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3370,17 +3370,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fuse box - Compact covered ATO/ATC fuse block 6-way</t>
+          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>3 identical</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor fuse boxes or new compact covered aftermarket</t>
+          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>PKR 11100-21000</t>
+          <t>PKR 54000-136000</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3405,22 +3405,22 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Covered body, firm lid, strong terminals</t>
+          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>229</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Reuse original Toyota-style boxes only if terminals are tight and no heat damage.</t>
+          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3440,34 +3440,34 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Prefer compact new covered fuse boxes online; keep original-style form factor.</t>
+          <t>Bilal Ganj only. Buy complete and bench-tested EPS set; no incomplete kits.</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://wellshop.pk/product/6-way-fuse-block-blade-fuse-box-holder-dc-12-32v-1-709607/</t>
+          <t>Bilal Ganj inspection only</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>BILAL_GANJ_ONLY</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
+          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1 complete kit</t>
+          <t>Full set</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
+          <t>New parts market only (no used donor plugs)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3477,37 +3477,37 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>PKR 54000-136000</t>
+          <t>PKR 12000-36000</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>images/20260321_235600.jpg</t>
+          <t>images/20260317_235150.jpg</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>BUY_IF_ENGINE_CODE_MATCH</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
+          <t>New only; no used/refurbished plugs</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
+          <t>20260317_235150.jpg</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
+          <t>No. Glow/heat plugs should be new only.</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -3527,34 +3527,34 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bilal Ganj only. Buy complete and bench-tested EPS set; no incomplete kits.</t>
+          <t>Buy new only (engine code/thread/reach confirmed first).</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Bilal Ganj inspection only</t>
+          <t>https://cruisercorps.com/products/ngk-3b-diesel-glow-plug-set-of-4</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>BILAL_GANJ_ONLY</t>
+          <t>BUY_AFTER_ENGINE_CODE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
+          <t>Local front leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Full set</t>
+          <t>2 packs</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>New parts market only (no used donor plugs)</t>
+          <t>Pakistan local spring manufacturer (Landhi preferred, Popular backup)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3564,47 +3564,47 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-36000</t>
+          <t>PKR 35000-90000</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>images/20260317_235150.jpg</t>
+          <t>images/20260324_004852.jpg</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>BUY_IF_ENGINE_CODE_MATCH</t>
+          <t>MEASURE_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>New only; no used/refurbished plugs</t>
+          <t>Buy only after measured fit confirmation</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20260317_235150.jpg</t>
+          <t>20260324_004852.jpg;20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>No. Glow/heat plugs should be new only.</t>
+          <t>Maybe. Keep existing only if no cracks, no sag, and bush eyes are within tolerance after mechanic inspection.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>MEASURE_FIRST_THEN_BUY</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Unchanged from active parts list.</t>
+          <t>Active local front leaf spring path.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3614,24 +3614,24 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Buy new only (engine code/thread/reach confirmed first).</t>
+          <t>Top local spring choice: Landhi Engineering Works (OEM + ISO) first, Popular Spring second; build to measured dimensions.</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://cruisercorps.com/products/ngk-3b-diesel-glow-plug-set-of-4</t>
+          <t>https://spring.com.pk/ ; https://popularspringind.com/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>BUY_AFTER_ENGINE_CODE</t>
+          <t>ACTIVE_SUSPENSION_CORE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Local front leaf spring pack (new, custom to measured dimensions)</t>
+          <t>Local rear leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220207.jpg</t>
+          <t>20260324_004852.jpg;20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Keep existing only if no cracks, no sag, and bush eyes are within tolerance after mechanic inspection.</t>
+          <t>Maybe. Keep existing only if no cracks, no inversion risk, and ride height is acceptable after load check.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Active local front leaf spring path.</t>
+          <t>Active local rear leaf spring path.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3718,17 +3718,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Local rear leaf spring pack (new, custom to measured dimensions)</t>
+          <t>Steering bushings - Steering linkage bush set</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2 packs</t>
+          <t>1 set</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Pakistan local spring manufacturer (Landhi preferred, Popular backup)</t>
+          <t>New hardware/electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3738,47 +3738,47 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>PKR 35000-90000</t>
+          <t>PKR 3000-12000</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>images/20260324_004852.jpg</t>
+          <t>images/20260406_031010.jpg</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_THEN_BUY_ACTIVE</t>
+          <t>INSPECT_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Buy only after measured fit confirmation</t>
+          <t>Condition-based quote</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220214.jpg</t>
+          <t>20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>230</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Keep existing only if no cracks, no inversion risk, and ride height is acceptable after load check.</t>
+          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_FIRST_THEN_BUY</t>
+          <t>BUY_ONLY_IF_PLAY_FOUND</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Active local rear leaf spring path.</t>
+          <t>Steering bushing only if wear/play confirmed.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3788,34 +3788,34 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Top local spring choice: Landhi Engineering Works (OEM + ISO) first, Popular Spring second; build to measured dimensions.</t>
+          <t>Use only if play exists. Prefer new bushings from verified supplier; avoid random used pieces.</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://spring.com.pk/ ; https://popularspringind.com/</t>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>ACTIVE_SUSPENSION_CORE</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Steering bushings - Steering linkage bush set</t>
+          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1 set</t>
+          <t>3 segments</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>New hardware/electrical market (not donor car)</t>
+          <t>Electrical workshop service (rework existing wires)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3825,47 +3825,47 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000</t>
+          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>images/20260406_031010.jpg</t>
+          <t>images/20260411_065030.jpg</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>INSPECT_THEN_BUY_ACTIVE</t>
+          <t>WORKSHOP_TASK</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Condition-based quote</t>
+          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20260406_031010.jpg</t>
+          <t>20260411_065030.jpg;20260321_235600.jpg</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>Electrical_Master</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
+          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>BUY_ONLY_IF_PLAY_FOUND</t>
+          <t>AS_LISTED</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Steering bushing only if wear/play confirmed.</t>
+          <t>Unchanged from active parts list.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3875,44 +3875,40 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Use only if play exists. Prefer new bushings from verified supplier; avoid random used pieces.</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
-        </is>
-      </c>
+          <t>No change.</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>KEEP_AS_ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
+          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>3 segments</t>
+          <t>10 rolls</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Electrical workshop service (rework existing wires)</t>
+          <t>New electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
+          <t>PKR 1500-4500</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3922,27 +3918,27 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP_TASK</t>
+          <t>BUY_NOW</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
+          <t>Good adhesive and heat tolerance, not brittle PVC</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260321_235600.jpg</t>
+          <t>20260411_065030.jpg</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Electrical_Master</t>
+          <t>SUB-17</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
+          <t>N/A consumable item; buy new.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3962,25 +3958,29 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>No change.</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr"/>
+          <t>Standard consumable; online purchase is fine.</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+        </is>
+      </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>KEEP_AS_ACTIVE</t>
+          <t>BUY_NOW</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
+          <t>Cloth harness loom tape (Tesa-style)</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>10 rolls</t>
+          <t>5 rolls</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>PKR 1500-4500</t>
+          <t>PKR 2500-9000</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Good adhesive and heat tolerance, not brittle PVC</t>
+          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>SUB-17</t>
+          <t>SUB-23</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Cloth harness loom tape (Tesa-style)</t>
+          <t>Firewall grommet assortment</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>5 rolls</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4077,17 +4077,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>PKR 2500-9000</t>
+          <t>PKR 2000-7000</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260411_143135.jpg</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -4097,17 +4097,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
+          <t>Hole ID/OD fit and thickness for firewall panels</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg</t>
+          <t>20260411_143135.jpg</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>SUB-23</t>
+          <t>SUB-11</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
+          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -4149,17 +4149,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Firewall grommet assortment</t>
+          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>New electrical market (not donor car)</t>
+          <t>Toyota donor car (Bilal Ganj)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4169,37 +4169,37 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PKR 2000-7000</t>
+          <t>PKR 60000-150000</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_143135.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>QUOTE_ONLY</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Hole ID/OD fit and thickness for firewall panels</t>
+          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>SUB-11</t>
+          <t>229-C1</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>N/A consumable item; buy new.</t>
+          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -4219,24 +4219,20 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Standard consumable; online purchase is fine.</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
-        </is>
-      </c>
+          <t>No change.</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>KEEP_AS_ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4256,7 +4252,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>PKR 60000-150000</t>
+          <t>PKR 55000-140000</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4271,7 +4267,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
+          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -4281,7 +4277,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>229-C1</t>
+          <t>229-C2</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -4319,7 +4315,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -4339,7 +4335,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PKR 55000-140000</t>
+          <t>PKR 50000-130000</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -4354,7 +4350,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
+          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -4364,7 +4360,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>229-C2</t>
+          <t>229-C3</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -4402,17 +4398,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
+          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1 complete kit</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor car (Bilal Ganj)</t>
+          <t>OME/EMU supplier or suspension fabricator</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4422,47 +4418,47 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PKR 50000-130000</t>
+          <t>PKR 12000-35000</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>images/20260321_235600.jpg</t>
+          <t>images/20260411_220214.jpg</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_ONLY</t>
+          <t>CONDITIONAL_LOCAL_ACTIVE</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
+          <t>Bracket geometry for your rear spring setup and axle travel clearance</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
+          <t>20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>229-C3</t>
+          <t>SUS-10</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
+          <t>Maybe. If current rear springs show no inversion tendency, can defer this item.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>BUY_ONLY_IF_INVERSION_RISK</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Unchanged from active parts list.</t>
+          <t>Only needed if spring inversion tendency appears.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4472,30 +4468,34 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>No change.</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr"/>
+          <t>Buy only if rear inversion tendency appears after spring setup.</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+        </is>
+      </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>KEEP_AS_ACTIVE</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
+          <t>Shock absorbers (new genuine, Pakistan high-quality path)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1 full set (front+rear)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>OME/EMU supplier or suspension fabricator</t>
+          <t>Agriauto genuine shocks (KYB/Gabriel global standards), authorized dealer network</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -4505,47 +4505,47 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-35000</t>
+          <t>PKR 25,000-80,000 (quote by exact model fitment)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_220214.jpg</t>
+          <t>images/20260324_004852.jpg</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>CONDITIONAL_LOCAL_ACTIVE</t>
+          <t>QUOTE_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Bracket geometry for your rear spring setup and axle travel clearance</t>
+          <t>Exact fitment length/mount type, new genuine packaging, invoice/warranty</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20260411_220214.jpg</t>
+          <t>20260324_004852.jpg;20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>SUS-10</t>
+          <t>SUS-11</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Maybe. If current rear springs show no inversion tendency, can defer this item.</t>
+          <t>Maybe. Replace if damping is weak, leaking, or ride control is poor.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>BUY_ONLY_IF_INVERSION_RISK</t>
+          <t>QUOTE_FIRST_THEN_BUY</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Only needed if spring inversion tendency appears.</t>
+          <t>Added to active suspension quality plan.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4555,102 +4555,15 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Buy only if rear inversion tendency appears after spring setup.</t>
+          <t>Best locally verifiable quality path is Agriauto genuine shocks (KYB/Gabriel standards, OEM-linked, 6-month warranty statement).</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+          <t>https://www.agriauto.com.pk/about-us/ ; https://www.agriauto.com.pk/products-post/genuine/ ; https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Shock absorbers (new genuine, Pakistan high-quality path)</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>1 full set (front+rear)</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Agriauto genuine shocks (KYB/Gabriel global standards), authorized dealer network</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>PKR 25,000-80,000 (quote by exact model fitment)</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>images/20260324_004852.jpg</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>QUOTE_THEN_BUY_ACTIVE</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Exact fitment length/mount type, new genuine packaging, invoice/warranty</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>20260324_004852.jpg;20260411_220207.jpg</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>SUS-11</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Maybe. Replace if damping is weak, leaking, or ride control is poor.</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>QUOTE_FIRST_THEN_BUY</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>Added to active suspension quality plan.</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>KEPT_IN_ACTIVE</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>Best locally verifiable quality path is Agriauto genuine shocks (KYB/Gabriel standards, OEM-linked, 6-month warranty statement).</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.agriauto.com.pk/about-us/ ; https://www.agriauto.com.pk/products-post/genuine/ ; https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>ACTIVE_SUSPENSION_CORE</t>
         </is>
